--- a/data/SQ单.xlsx
+++ b/data/SQ单.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\11391\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\文档\数据标准智能体 2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449FCF33-3D8E-46A6-B997-FB6E0B006370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E839DE5-DCDE-4233-9BE4-791547991841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$AD$24</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="96">
   <si>
     <t>贴源接口(必填)</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -152,6 +156,202 @@
   </si>
   <si>
     <t>说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字段中文名</t>
+  </si>
+  <si>
+    <t>字段所属类型</t>
+  </si>
+  <si>
+    <t>业务含义</t>
+  </si>
+  <si>
+    <t>枚举值</t>
+  </si>
+  <si>
+    <t>客户名称</t>
+  </si>
+  <si>
+    <t>文本类</t>
+  </si>
+  <si>
+    <t>开户日期</t>
+  </si>
+  <si>
+    <t>日期时间类</t>
+  </si>
+  <si>
+    <t>开户的日期</t>
+  </si>
+  <si>
+    <t>手机号码</t>
+  </si>
+  <si>
+    <t>客户手机号</t>
+  </si>
+  <si>
+    <t>客户状态</t>
+  </si>
+  <si>
+    <t>代码枚举类</t>
+  </si>
+  <si>
+    <t>标识客户在系统中的当前状态，包括正常、冻结、注销等</t>
+  </si>
+  <si>
+    <t>01-正常;02-冻结;03-注销</t>
+  </si>
+  <si>
+    <t>交易金额</t>
+  </si>
+  <si>
+    <t>数值类</t>
+  </si>
+  <si>
+    <t>记录一笔交易的实际发生金额，单位为元</t>
+  </si>
+  <si>
+    <t>第二结论类型</t>
+  </si>
+  <si>
+    <t>01-通过;02-拒绝</t>
+  </si>
+  <si>
+    <t>CDA规则结果</t>
+  </si>
+  <si>
+    <t>CDA的规则结果</t>
+  </si>
+  <si>
+    <t>01-命中;02-未命中</t>
+  </si>
+  <si>
+    <t>CDA规则结果字段</t>
+  </si>
+  <si>
+    <t>转案欺诈类型</t>
+  </si>
+  <si>
+    <t>指转案欺诈的不同类别</t>
+  </si>
+  <si>
+    <t>01-欺诈;02-正常</t>
+  </si>
+  <si>
+    <t>信用风险评估系统CDA引擎生成的规则判定结果，用于自动审批决策</t>
+  </si>
+  <si>
+    <t>标记案件转案过程中涉及的欺诈行为分类，由风控系统自动识别</t>
+  </si>
+  <si>
+    <t>记录客户的电子邮箱地址</t>
+  </si>
+  <si>
+    <t>证件类型</t>
+  </si>
+  <si>
+    <t>标识客户使用的证件类型</t>
+  </si>
+  <si>
+    <t>身份证;护照;军官证</t>
+  </si>
+  <si>
+    <t>账户余额</t>
+  </si>
+  <si>
+    <t>银行卡号</t>
+  </si>
+  <si>
+    <t>字符型</t>
+  </si>
+  <si>
+    <t>记录客户绑定的银行卡卡号，用于资金划转</t>
+  </si>
+  <si>
+    <t>是否VIP</t>
+  </si>
+  <si>
+    <t>布尔型</t>
+  </si>
+  <si>
+    <t>标识客户是否为VIP用户</t>
+  </si>
+  <si>
+    <t>支付方式</t>
+  </si>
+  <si>
+    <t>记录客户选择的支付方式类型</t>
+  </si>
+  <si>
+    <t>1.现金 2.银行卡 3.支票 4.汇款</t>
+  </si>
+  <si>
+    <t>性别</t>
+  </si>
+  <si>
+    <t>标识客户的性别信息</t>
+  </si>
+  <si>
+    <t>男/女</t>
+  </si>
+  <si>
+    <t>信用等级</t>
+  </si>
+  <si>
+    <t>反映客户的信用评级，由风控系统定期计算更新</t>
+  </si>
+  <si>
+    <t>(A)优秀 (B)良好 (C)一般 (D)较差</t>
+  </si>
+  <si>
+    <t>币种代码</t>
+  </si>
+  <si>
+    <t>编码类</t>
+  </si>
+  <si>
+    <t>标识交易使用的货币类型代码，遵循ISO 4217标准</t>
+  </si>
+  <si>
+    <t>01：人民币 02：美元 03：欧元</t>
+  </si>
+  <si>
+    <t>是否冻结</t>
+  </si>
+  <si>
+    <t>标志类</t>
+  </si>
+  <si>
+    <t>标识账户是否被冻结，冻结后无法进行交易操作</t>
+  </si>
+  <si>
+    <t>Y-是;N-否</t>
+  </si>
+  <si>
+    <t>交易状态</t>
+  </si>
+  <si>
+    <t>记录交易的当前处理状态</t>
+  </si>
+  <si>
+    <t>01-成功;02-失败;03-处理中</t>
+  </si>
+  <si>
+    <t>客户名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>域和字段不符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>域和数据示例不符</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否枚举填写有误</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -480,14 +680,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AC24"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="28" max="28" width="13.88671875" customWidth="1"/>
-    <col min="29" max="29" width="14.5546875" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.88671875" customWidth="1"/>
+    <col min="28" max="28" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
@@ -518,14 +719,13 @@
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
-      <c r="AB1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -596,34 +796,660 @@
         <v>22</v>
       </c>
       <c r="X2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Z2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AB2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AC2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AD2" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N3" t="s">
+        <v>93</v>
+      </c>
+      <c r="O3" t="s">
+        <v>36</v>
+      </c>
+      <c r="R3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N4" t="s">
+        <v>93</v>
+      </c>
+      <c r="O4" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" t="s">
+        <v>39</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O5" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6" t="s">
+        <v>43</v>
+      </c>
+      <c r="R6" t="s">
+        <v>44</v>
+      </c>
+      <c r="W6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O7" t="s">
+        <v>47</v>
+      </c>
+      <c r="R7" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N8" t="s">
+        <v>94</v>
+      </c>
+      <c r="O8" t="s">
+        <v>50</v>
+      </c>
+      <c r="R8" t="s">
+        <v>44</v>
+      </c>
+      <c r="W8" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9" t="s">
+        <v>52</v>
+      </c>
+      <c r="R9" t="s">
+        <v>44</v>
+      </c>
+      <c r="W9" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N10">
+        <v>1</v>
+      </c>
+      <c r="O10" t="s">
+        <v>52</v>
+      </c>
+      <c r="R10" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N11" t="s">
+        <v>95</v>
+      </c>
+      <c r="O11" t="s">
+        <v>56</v>
+      </c>
+      <c r="R11" t="s">
+        <v>44</v>
+      </c>
+      <c r="W11" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N12" t="s">
+        <v>93</v>
+      </c>
+      <c r="O12" t="s">
+        <v>52</v>
+      </c>
+      <c r="R12" t="s">
+        <v>44</v>
+      </c>
+      <c r="W12" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="O13" t="s">
+        <v>56</v>
+      </c>
+      <c r="R13" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N14" t="s">
+        <v>93</v>
+      </c>
+      <c r="R14" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="O15" t="s">
+        <v>62</v>
+      </c>
+      <c r="W15" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="N16" t="s">
+        <v>93</v>
+      </c>
+      <c r="O16" t="s">
+        <v>65</v>
+      </c>
+      <c r="R16" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="14:25" x14ac:dyDescent="0.25">
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="O17" t="s">
+        <v>66</v>
+      </c>
+      <c r="R17" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="14:25" x14ac:dyDescent="0.25">
+      <c r="N18">
+        <v>1</v>
+      </c>
+      <c r="O18" t="s">
+        <v>69</v>
+      </c>
+      <c r="R18" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="14:25" x14ac:dyDescent="0.25">
+      <c r="N19" t="s">
+        <v>93</v>
+      </c>
+      <c r="O19" t="s">
+        <v>72</v>
+      </c>
+      <c r="R19" t="s">
+        <v>44</v>
+      </c>
+      <c r="W19" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="14:25" x14ac:dyDescent="0.25">
+      <c r="N20" t="s">
+        <v>95</v>
+      </c>
+      <c r="O20" t="s">
+        <v>75</v>
+      </c>
+      <c r="R20" t="s">
+        <v>44</v>
+      </c>
+      <c r="W20" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="21" spans="14:25" x14ac:dyDescent="0.25">
+      <c r="N21">
+        <v>1</v>
+      </c>
+      <c r="O21" t="s">
+        <v>78</v>
+      </c>
+      <c r="R21" t="s">
+        <v>44</v>
+      </c>
+      <c r="W21" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="14:25" x14ac:dyDescent="0.25">
+      <c r="N22" t="s">
+        <v>94</v>
+      </c>
+      <c r="O22" t="s">
+        <v>81</v>
+      </c>
+      <c r="R22" t="s">
+        <v>82</v>
+      </c>
+      <c r="W22" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="14:25" x14ac:dyDescent="0.25">
+      <c r="N23" t="s">
+        <v>94</v>
+      </c>
+      <c r="O23" t="s">
+        <v>85</v>
+      </c>
+      <c r="R23" t="s">
+        <v>86</v>
+      </c>
+      <c r="W23" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="14:25" x14ac:dyDescent="0.25">
+      <c r="N24" t="s">
+        <v>94</v>
+      </c>
+      <c r="O24" t="s">
+        <v>89</v>
+      </c>
+      <c r="R24" t="s">
+        <v>44</v>
+      </c>
+      <c r="W24" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="I1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="I1:Z1"/>
+    <mergeCell ref="AA1:AC1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A075948-65A7-4713-8857-B786F27E393C}">
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>75</v>
+      </c>
+      <c r="B19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>